--- a/data/信用债发行汇总_2026-08-18.xlsx
+++ b/data/信用债发行汇总_2026-08-18.xlsx
@@ -1340,7 +1340,9 @@
           <t>1.80 ~ 2.80</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr"/>
+      <c r="H3" s="4" t="n">
+        <v>2.1</v>
+      </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
           <t>凉山州发展(控股)集团有限责任公司</t>
